--- a/docs/mokxya-ai/reviews/mai07_v3/review_operations/reviewer_packages/PRODUCT_POLICY/round_a/MokXya_MAI07_V3__PRODUCT_POLICY__ROUND_A__BATCH_03_of_10.xlsx
+++ b/docs/mokxya-ai/reviews/mai07_v3/review_operations/reviewer_packages/PRODUCT_POLICY/round_a/MokXya_MAI07_V3__PRODUCT_POLICY__ROUND_A__BATCH_03_of_10.xlsx
@@ -586,7 +586,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>declaration_independent</t>
+          <t>declaration_independent_from_other_reviewers</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
